--- a/backend-excel/initial-data/accounts.xlsx
+++ b/backend-excel/initial-data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$s37Hj7N4qHuQye0OFn7abOBbCQeHhhm5LO0YahTv.GEtOgpMFUQ9u</v>
+        <v>$2a$10$EJkfja8nUn0kWniVg2pkDeM79pnPKX3FHShg5z1s/Uq9/HkziDH4m</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$wuiKYzuSTyfa2aUWxEfq1umIh1OcNrNDPI1hODLZV13C8L3PC8wE.</v>
+        <v>$2a$10$TLTlL/3URkhZHVk88894F.kwXo.zW78ww6vuCF5ZGvoBDxIZqIWFW</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$9UlVbs6qO.99Bd4NIBE6GunoM6/lVIqkvYn/RY2CxCbRA21/BVk6O</v>
+        <v>$2a$10$QsjgAKA5loONjFUhCOGsd.uLSvGGr77rxN7Dl3C4mjgQ7S2Xi1a.2</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$hb/fGSTMVmSdaAuJFscqGec/PQEyzpw/7S0naJTFnFxeyIsUdLweW</v>
+        <v>$2a$10$jkQ3sMKkbhFANbhXoNuvs.PQdJmggra6rJ/dEnc0elYJJRYHdYJT6</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/initial-data/accounts.xlsx
+++ b/backend-excel/initial-data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$EJkfja8nUn0kWniVg2pkDeM79pnPKX3FHShg5z1s/Uq9/HkziDH4m</v>
+        <v>$2a$10$QUeBocwrNV.0rN8pLMtoMO/kNKUcQWZ9McuSUMJSfhM/7fxnwx3EW</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$TLTlL/3URkhZHVk88894F.kwXo.zW78ww6vuCF5ZGvoBDxIZqIWFW</v>
+        <v>$2a$10$LzUY3..u62waWJwxfnLmt.3aJS2TOoqBB/882vD6FFQ6lU8WrdJQG</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$QsjgAKA5loONjFUhCOGsd.uLSvGGr77rxN7Dl3C4mjgQ7S2Xi1a.2</v>
+        <v>$2a$10$uVHuCt3ymtm1UTOWzhhCeeNnB4xLekhWwvi.V0XrNseCt1Gm9D36O</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$jkQ3sMKkbhFANbhXoNuvs.PQdJmggra6rJ/dEnc0elYJJRYHdYJT6</v>
+        <v>$2a$10$fmFbZJHw3HxoCdUCnVOJb.XzySL8e9RMHenN3vzg/bnj.b9IGn2J2</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/initial-data/accounts.xlsx
+++ b/backend-excel/initial-data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$QUeBocwrNV.0rN8pLMtoMO/kNKUcQWZ9McuSUMJSfhM/7fxnwx3EW</v>
+        <v>$2a$10$9HpgCwgN3eI2m3PekH.Ztu9qot1hsC1kS8sFjBQdLkfktvUnBTsty</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$LzUY3..u62waWJwxfnLmt.3aJS2TOoqBB/882vD6FFQ6lU8WrdJQG</v>
+        <v>$2a$10$D4VO3B7eplyFuAy7dth2aOO2H/a21VXEr2EhUNnVVzLxfzfFQk6k.</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$uVHuCt3ymtm1UTOWzhhCeeNnB4xLekhWwvi.V0XrNseCt1Gm9D36O</v>
+        <v>$2a$10$IPt3KMUCnPt9zXMx9yZPp.8U.jOC1gMcrWbrDdNOlVQqmBp6xDhXa</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$fmFbZJHw3HxoCdUCnVOJb.XzySL8e9RMHenN3vzg/bnj.b9IGn2J2</v>
+        <v>$2a$10$BApe2cDr5pl6tBiZzcD9LOLGVh6gcaXd8tdFgUg/S6CNs52UmHvMC</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/initial-data/accounts.xlsx
+++ b/backend-excel/initial-data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$9HpgCwgN3eI2m3PekH.Ztu9qot1hsC1kS8sFjBQdLkfktvUnBTsty</v>
+        <v>$2a$10$9qbCwNF3M37kQGO2Q7A.meIpOdyZDf/AQB/tr6JI0efGsSx62rvwi</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$D4VO3B7eplyFuAy7dth2aOO2H/a21VXEr2EhUNnVVzLxfzfFQk6k.</v>
+        <v>$2a$10$7102X88SMhaXjgvcS4uPNeKLDaB.BEuvYREwr0QMAlh7Ap1MQumdC</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$IPt3KMUCnPt9zXMx9yZPp.8U.jOC1gMcrWbrDdNOlVQqmBp6xDhXa</v>
+        <v>$2a$10$a2Nn2dlp6NDHGujxm0iKS.mcuD9CTI7zBszGftqYo8305rapG6ejO</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$BApe2cDr5pl6tBiZzcD9LOLGVh6gcaXd8tdFgUg/S6CNs52UmHvMC</v>
+        <v>$2a$10$54LjT1jWokPyd5jdxHbJVOsB8NWv9h8BcGXu6mmaQcyn0KM6Hq1mS</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>
